--- a/reports/pdf_change_20260805.xlsx
+++ b/reports/pdf_change_20260805.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,001억   ·   현금 114억(2.7%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 5종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,232억   ·   현금 114억(2.7%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>443248640</v>
+        <v>444114360</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-46</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-420638720</v>
+        <v>-421460280</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>27</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1415577600</v>
+        <v>1418342400</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-9</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1220198400</v>
+        <v>-1222581600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4647936000</v>
+        <v>4657014000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-4</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-198246400</v>
+        <v>-198633600</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>648960000</v>
+        <v>650227500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-3</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1181184000</v>
+        <v>-1183491000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>891289600</v>
+        <v>893030400</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,369억   ·   현금 14억(0.4%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 1종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,729억   ·   현금 14억(0.4%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -958,7 +958,7 @@
         <v>57</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>7974756000</v>
+        <v>7959537000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 50억(2.1%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 1종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,367억   ·   현금 49억(2.1%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1075,7 +1075,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2020656000</v>
+        <v>2011845000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,992억   ·   현금 13억(0.6%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 3종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,168억   ·   현금 13억(0.6%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1285,7 +1285,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억   ·   현금 7억(2.8%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 4종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 261억   ·   현금 7억(2.6%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1381,11 +1381,11 @@
         <v>31</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>63356250</v>
+        <v>63123750</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.91%</t>
+          <t>2.45%→2.69%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1402,11 +1402,11 @@
         <v>-98</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-76807500</v>
+        <v>-91581000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>1.80%→1.46%</t>
+          <t>1.99%→1.62%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1418,23 +1418,23 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>42165000</v>
+        <v>56700000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.82%</t>
+          <t>2.83%→3.04%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -1446,11 +1446,11 @@
         <v>-22</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-26383500</v>
+        <v>-32488500</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2.73%→2.60%</t>
+          <t>3.12%→2.98%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1462,23 +1462,23 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>56475000</v>
+        <v>43425000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>3.03%→3.26%</t>
+          <t>2.54%→2.70%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -1490,11 +1490,11 @@
         <v>-14</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-25515000</v>
+        <v>-30030000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>6.26%→6.12%</t>
+          <t>6.84%→6.69%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1513,11 +1513,11 @@
         <v>4</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>95250000</v>
+        <v>104100000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.81%</t>
+          <t>1.43%→1.84%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 13억(2.5%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 5종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 501억   ·   현금 12억(2.5%)      당일 2026-08-05  vs  전영업일 2026-08-04      매수 5종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1630,7 +1630,7 @@
         <v>34</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>246758400</v>
+        <v>237945600</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>-9</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-387576000</v>
+        <v>-373734000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>33</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>986832000</v>
+        <v>951588000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>-8</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-166476800</v>
+        <v>-160531200</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>270144000</v>
+        <v>260496000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>21</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>258484800</v>
+        <v>249253200</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>16</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>214681600</v>
+        <v>207014400</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_change_20260805.xlsx
+++ b/reports/pdf_change_20260805.xlsx
@@ -1418,23 +1418,23 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>56700000</v>
+        <v>43425000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>2.83%→3.04%</t>
+          <t>2.54%→2.70%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -1462,23 +1462,23 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>43425000</v>
+        <v>56700000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>2.54%→2.70%</t>
+          <t>2.83%→3.04%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
